--- a/oct2026-results tables/top10_by_dataset.xlsx
+++ b/oct2026-results tables/top10_by_dataset.xlsx
@@ -390,46 +390,46 @@
         </is>
       </c>
       <c r="C2">
-        <v>32105</v>
+        <v>35459</v>
       </c>
       <c r="D2">
-        <v>30.13365621069625</v>
+        <v>31.91370636</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Cuba</t>
+          <t>Australia</t>
         </is>
       </c>
       <c r="C3">
-        <v>18914</v>
+        <v>18390</v>
       </c>
       <c r="D3">
-        <v>34.83369553206379</v>
+        <v>29.91022055</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Cuba</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Australia</t>
+          <t>Cuba</t>
         </is>
       </c>
       <c r="C4">
-        <v>18390</v>
+        <v>17965</v>
       </c>
       <c r="D4">
-        <v>29.91022054518249</v>
+        <v>33.06036069</v>
       </c>
     </row>
     <row r="5">
@@ -447,7 +447,7 @@
         <v>16150</v>
       </c>
       <c r="D5">
-        <v>23.24744494026198</v>
+        <v>23.24744494</v>
       </c>
     </row>
     <row r="6">
@@ -465,7 +465,7 @@
         <v>15196</v>
       </c>
       <c r="D6">
-        <v>45.04921143128187</v>
+        <v>45.04921143</v>
       </c>
     </row>
     <row r="7">
@@ -483,7 +483,7 @@
         <v>5590</v>
       </c>
       <c r="D7">
-        <v>25.86645689695063</v>
+        <v>25.8664569</v>
       </c>
     </row>
     <row r="8">
@@ -501,7 +501,7 @@
         <v>4485</v>
       </c>
       <c r="D8">
-        <v>31.39437211255775</v>
+        <v>31.39437211</v>
       </c>
     </row>
     <row r="9">
@@ -519,7 +519,7 @@
         <v>3949</v>
       </c>
       <c r="D9">
-        <v>41.09261186264308</v>
+        <v>41.09261186</v>
       </c>
     </row>
     <row r="10">
@@ -537,7 +537,7 @@
         <v>3432</v>
       </c>
       <c r="D10">
-        <v>32.17399456266992</v>
+        <v>32.17399456</v>
       </c>
     </row>
     <row r="11">
@@ -555,7 +555,7 @@
         <v>2531</v>
       </c>
       <c r="D11">
-        <v>29.03188804771737</v>
+        <v>29.03188805</v>
       </c>
     </row>
   </sheetData>

--- a/oct2026-results tables/top10_by_dataset.xlsx
+++ b/oct2026-results tables/top10_by_dataset.xlsx
@@ -10,6 +10,7 @@
     <sheet name="aca_wcmc" sheetId="1" r:id="rId1"/>
     <sheet name="wcmc" sheetId="2" r:id="rId2"/>
     <sheet name="aca_coral" sheetId="3" r:id="rId3"/>
+    <sheet name="aca_wcmc_ssp585" sheetId="4" r:id="rId4"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -623,7 +624,7 @@
         <v>7734</v>
       </c>
       <c r="D3">
-        <v>42.58341592335646</v>
+        <v>42.5834159233565</v>
       </c>
     </row>
     <row r="4">
@@ -641,7 +642,7 @@
         <v>6424</v>
       </c>
       <c r="D4">
-        <v>22.62449813340847</v>
+        <v>22.6244981334085</v>
       </c>
     </row>
     <row r="5">
@@ -659,7 +660,7 @@
         <v>2618</v>
       </c>
       <c r="D5">
-        <v>24.45357743321502</v>
+        <v>24.453577433215</v>
       </c>
     </row>
     <row r="6">
@@ -677,7 +678,7 @@
         <v>2209</v>
       </c>
       <c r="D6">
-        <v>46.85047720042418</v>
+        <v>46.8504772004242</v>
       </c>
     </row>
     <row r="7">
@@ -695,7 +696,7 @@
         <v>1624</v>
       </c>
       <c r="D7">
-        <v>33.19027181688126</v>
+        <v>33.1902718168813</v>
       </c>
     </row>
     <row r="8">
@@ -713,7 +714,7 @@
         <v>1477</v>
       </c>
       <c r="D8">
-        <v>36.18324350808427</v>
+        <v>36.1832435080843</v>
       </c>
     </row>
     <row r="9">
@@ -731,7 +732,7 @@
         <v>1364</v>
       </c>
       <c r="D9">
-        <v>36.97478991596638</v>
+        <v>36.9747899159664</v>
       </c>
     </row>
     <row r="10">
@@ -749,7 +750,7 @@
         <v>1356</v>
       </c>
       <c r="D10">
-        <v>31.69705469845722</v>
+        <v>31.6970546984572</v>
       </c>
     </row>
     <row r="11">
@@ -767,7 +768,7 @@
         <v>1179</v>
       </c>
       <c r="D11">
-        <v>21.64494217000184</v>
+        <v>21.6449421700018</v>
       </c>
     </row>
   </sheetData>
@@ -817,7 +818,7 @@
         <v>6069</v>
       </c>
       <c r="D2">
-        <v>24.74415949769642</v>
+        <v>24.7441594976964</v>
       </c>
     </row>
     <row r="3">
@@ -835,7 +836,7 @@
         <v>5248</v>
       </c>
       <c r="D3">
-        <v>40.55328027200371</v>
+        <v>40.5532802720037</v>
       </c>
     </row>
     <row r="4">
@@ -853,7 +854,7 @@
         <v>3404</v>
       </c>
       <c r="D4">
-        <v>29.57942301007995</v>
+        <v>29.57942301008</v>
       </c>
     </row>
     <row r="5">
@@ -889,7 +890,7 @@
         <v>1517</v>
       </c>
       <c r="D6">
-        <v>45.78931482040447</v>
+        <v>45.7893148204045</v>
       </c>
     </row>
     <row r="7">
@@ -907,7 +908,7 @@
         <v>1446</v>
       </c>
       <c r="D7">
-        <v>22.86527514231499</v>
+        <v>22.865275142315</v>
       </c>
     </row>
     <row r="8">
@@ -925,7 +926,7 @@
         <v>1311</v>
       </c>
       <c r="D8">
-        <v>30.06880733944954</v>
+        <v>30.0688073394495</v>
       </c>
     </row>
     <row r="9">
@@ -943,7 +944,7 @@
         <v>932</v>
       </c>
       <c r="D9">
-        <v>28.21677263094157</v>
+        <v>28.2167726309416</v>
       </c>
     </row>
     <row r="10">
@@ -979,7 +980,219 @@
         <v>675</v>
       </c>
       <c r="D11">
-        <v>37.83632286995515</v>
+        <v>37.8363228699551</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:D11"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" s="1" customFormat="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>eez_country</t>
+        </is>
+      </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>eez_countries_territories</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>x50reefs_plus_km2</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>x50reefs_plus_pct</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Bahamas</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Bahamas</t>
+        </is>
+      </c>
+      <c r="C2">
+        <v>34302</v>
+      </c>
+      <c r="D2">
+        <v>30.87210872</v>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>Australia</t>
+        </is>
+      </c>
+      <c r="C3">
+        <v>18554</v>
+      </c>
+      <c r="D3">
+        <v>30.1764658</v>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>Cuba</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>Cuba</t>
+        </is>
+      </c>
+      <c r="C4">
+        <v>18182</v>
+      </c>
+      <c r="D4">
+        <v>33.4596982</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>Indonesia</t>
+        </is>
+      </c>
+      <c r="C5">
+        <v>16158</v>
+      </c>
+      <c r="D5">
+        <v>23.25929551</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>Philippines</t>
+        </is>
+      </c>
+      <c r="C6">
+        <v>14810</v>
+      </c>
+      <c r="D6">
+        <v>43.90619905</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Papua New Guinea</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Papua New Guinea</t>
+        </is>
+      </c>
+      <c r="C7">
+        <v>6203</v>
+      </c>
+      <c r="D7">
+        <v>28.70164723</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Saudi Arabia</t>
+        </is>
+      </c>
+      <c r="C8">
+        <v>4487</v>
+      </c>
+      <c r="D8">
+        <v>31.40617344</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>Fiji</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Fiji</t>
+        </is>
+      </c>
+      <c r="C9">
+        <v>3399</v>
+      </c>
+      <c r="D9">
+        <v>31.8735934</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>Solomon Islands</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Solomon Islands</t>
+        </is>
+      </c>
+      <c r="C10">
+        <v>3398</v>
+      </c>
+      <c r="D10">
+        <v>35.36268082</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>France</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>French Polynesia</t>
+        </is>
+      </c>
+      <c r="C11">
+        <v>2554</v>
+      </c>
+      <c r="D11">
+        <v>29.29571003</v>
       </c>
     </row>
   </sheetData>
